--- a/public/files/Data_By_Towns_Index/Burlington/Eastampton Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Eastampton Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,261 +425,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATEL, RAJ AND HITEKSHA</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1313 MONMOUTH RD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-74.7632175</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.0062709</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJERc-_D1GwYkRPHwpKcEUiXk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL, ANANTKUMAR S &amp; KUSH A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17 BRIDGE BLVD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-74.74445109999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.0060832</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJ7Spjz2dGwYkRP5sKkgwhmQY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PARIKH, SONAL AND DIPAK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30 MUSEUM DR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.7419594</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.0047887</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJD9vTc2dGwYkRjk2dIad7WSc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BHATT, REENA S AND SAMIR R</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>46 TOWER BLVD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-74.74085049999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40.004592</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJAcksQmdGwYkRHCzJewVZR3k</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATEL, RAJENDRAKUMAR AND JIGISHABEN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>43 COLISEUM DR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-74.74033299999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.0032039</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJJ-iZ8F1GwYkRZuikvVC2x6E</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHAH, MIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>66 TOWER BLVD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eastampton Township</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-74.74080699999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40.00302</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJyVGE7V1GwYkRpDIaj-0rBN4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>MEHTA, HEMANG R.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>84 BRIDGE BLVD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Eastampton Township</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mehta</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-74.7440766</v>
+      </c>
+      <c r="G8" t="n">
         <v>40.0109832</v>
       </c>
-      <c r="G2" t="n">
-        <v>-74.7440766</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PATEL, ANANTKUMAR S &amp; KUSH A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>17 BRIDGE BLVD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJdxuPl2VGwYkRipmic9oE5Fg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SHAH, RAM N &amp; AMISHA R</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3 WOODHURST CT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Eastampton Township</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>40.0060832</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-74.74445109999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PATEL, PANKAJ &amp; KOKILA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1005 WOODLANE RD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Eastampton Township</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>40.0073</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-74.77369999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PATEL, RAJENDRAKUMAR AND JIGISHABEN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>43 COLISEUM DR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Eastampton Township</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>40.0032039</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-74.74033299999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SHAH, RAM N &amp; AMISHA R</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3 WOODHURST CT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Eastampton Township</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-74.7481367</v>
+      </c>
+      <c r="G9" t="n">
         <v>39.9941268</v>
       </c>
-      <c r="G6" t="n">
-        <v>-74.7481367</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BHATT, REENA S AND SAMIR R</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>46 TOWER BLVD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Eastampton Township</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bhatt</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>40.004592</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-74.74085049999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PARIKH, SONAL AND DIPAK</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>30 MUSEUM DR</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Eastampton Township</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Parikh</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>40.0047887</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-74.7419594</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJTXcbg09GwYkRtqJRAKCPXOE</t>
+        </is>
       </c>
     </row>
   </sheetData>
